--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>49021</t>
   </si>
@@ -94,7 +94,7 @@
     <t>Fecha de término del periodo que se informa</t>
   </si>
   <si>
-    <t>Descripción breve, clara y precisa que dé cuenta del contenido de la información</t>
+    <t>Descripción breve, clara y precisa del contenido de la información (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de elaboración </t>
@@ -115,31 +115,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>3FBA9A7BAA4D52DDB74D4DEE202E3603</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>15/05/2022</t>
-  </si>
-  <si>
-    <t>Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de abril del 2022 al 30 de junio del 2022, el Colegio de Bachilleres del Estado de Tlaxcala no recibió solicitudes de información Pública de oficio.</t>
+    <t>AA49F3650A91159CAC197EC115263A8A</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Área de Trasnparencia</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de abril del 2023 al 30 de junio del 2023, el Colegio de Bachilleres del Estado de Tlaxcala no recibió solicitudes de información Pública de oficio.</t>
   </si>
 </sst>
 </file>
@@ -535,17 +532,17 @@
   <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="90.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="121.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="144.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="139.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
@@ -713,22 +710,22 @@
         <v>34</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
